--- a/data/trans_orig/IP2905_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2905_2023-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53776</t>
+          <t>53836</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71105</t>
+          <t>70596</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56626</t>
+          <t>56261</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88197</t>
+          <t>88911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116159</t>
+          <t>116911</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>150629</t>
+          <t>151727</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,83%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41953</t>
+          <t>42462</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59282</t>
+          <t>59222</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48154</t>
+          <t>47440</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79725</t>
+          <t>80090</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98780</t>
+          <t>97682</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133250</t>
+          <t>132498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,12%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91787</t>
+          <t>92315</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116305</t>
+          <t>116820</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>122270</t>
+          <t>120551</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150934</t>
+          <t>149270</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>218774</t>
+          <t>220178</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>258796</t>
+          <t>260726</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,43%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>68705</t>
+          <t>68190</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93223</t>
+          <t>92695</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95472</t>
+          <t>97136</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>124136</t>
+          <t>125855</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>172620</t>
+          <t>170690</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>212642</t>
+          <t>211238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,96%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54982</t>
+          <t>54851</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78006</t>
+          <t>78330</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65018</t>
+          <t>67219</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94024</t>
+          <t>94609</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>129701</t>
+          <t>128656</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164283</t>
+          <t>164408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82107</t>
+          <t>81783</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105131</t>
+          <t>105262</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>87132</t>
+          <t>86547</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116138</t>
+          <t>113937</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>176986</t>
+          <t>176861</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>211568</t>
+          <t>212613</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>62,3%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62927</t>
+          <t>64427</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83932</t>
+          <t>85173</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77691</t>
+          <t>77955</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101496</t>
+          <t>101177</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>147801</t>
+          <t>147131</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>179048</t>
+          <t>178956</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,34%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76452</t>
+          <t>75211</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97457</t>
+          <t>95957</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73636</t>
+          <t>73955</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97441</t>
+          <t>97177</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156468</t>
+          <t>156560</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>187715</t>
+          <t>188385</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>56,15%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>284750</t>
+          <t>286377</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>328568</t>
+          <t>329456</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>347770</t>
+          <t>348861</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>404953</t>
+          <t>404445</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>648831</t>
+          <t>646341</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>719338</t>
+          <t>719224</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,98%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>289997</t>
+          <t>289109</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>333815</t>
+          <t>332188</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>334091</t>
+          <t>334599</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>391274</t>
+          <t>390183</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>638271</t>
+          <t>638385</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>708778</t>
+          <t>711268</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,39%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2905_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP2905_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>64343</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>52780</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>78427</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,53%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>43,09%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>64,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>62751</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>53836</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>70596</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>55,5%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,62%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>62,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>70151</t>
+          <t>64924</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56261</t>
+          <t>56044</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88911</t>
+          <t>74587</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>51,45%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>132903</t>
+          <t>129267</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>116911</t>
+          <t>115269</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>151727</t>
+          <t>145485</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,81%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>58146</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>44062</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>69709</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,47%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>35,97%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>56,91%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>50307</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42462</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>59222</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>44,5%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>37,56%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>52,38%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66200</t>
+          <t>51821</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47440</t>
+          <t>42158</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80090</t>
+          <t>60701</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>116506</t>
+          <t>109967</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97682</t>
+          <t>93749</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132498</t>
+          <t>123965</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122489</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122489</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122489</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>113058</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>113058</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>113058</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136351</t>
+          <t>116745</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136351</t>
+          <t>116745</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136351</t>
+          <t>116745</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>249409</t>
+          <t>239234</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>249409</t>
+          <t>239234</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>249409</t>
+          <t>239234</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>125766</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>111013</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>141472</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>54,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>48,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>61,49%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>104033</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>92315</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>116820</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>56,23%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>49,9%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>63,14%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>136122</t>
+          <t>98840</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>120551</t>
+          <t>87598</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>149270</t>
+          <t>110509</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>240155</t>
+          <t>224606</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>220178</t>
+          <t>205804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>260726</t>
+          <t>242969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>59,34%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>104318</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>88612</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>119071</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>45,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>38,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>51,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>80977</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>68190</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>92695</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>43,77%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>36,86%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>50,1%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>110284</t>
+          <t>80547</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>97136</t>
+          <t>68878</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>125855</t>
+          <t>91789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>191261</t>
+          <t>184865</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>170690</t>
+          <t>166502</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>211238</t>
+          <t>203667</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,74%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>230084</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>230084</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>230084</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>185010</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>185010</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>185010</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>246406</t>
+          <t>179387</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>246406</t>
+          <t>179387</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>246406</t>
+          <t>179387</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>431416</t>
+          <t>409471</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>431416</t>
+          <t>409471</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>431416</t>
+          <t>409471</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>69962</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>57138</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>83995</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>42,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>34,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>51,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>66055</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>54851</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>78330</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>41,26%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>34,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>48,92%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>80116</t>
+          <t>59134</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67219</t>
+          <t>48688</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94609</t>
+          <t>70183</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>146171</t>
+          <t>129096</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>128656</t>
+          <t>114561</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164408</t>
+          <t>147939</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>46,87%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>94695</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>80662</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>107519</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>57,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>48,99%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>65,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>94058</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>81783</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>105262</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>58,74%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>51,08%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>65,74%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>101040</t>
+          <t>91856</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86547</t>
+          <t>80807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113937</t>
+          <t>102302</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>195098</t>
+          <t>186551</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>176861</t>
+          <t>167708</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>212613</t>
+          <t>201086</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>63,71%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>164657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>164657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>164657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>160113</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>160113</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>160113</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181156</t>
+          <t>150990</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181156</t>
+          <t>150990</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181156</t>
+          <t>150990</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>341269</t>
+          <t>315647</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>341269</t>
+          <t>315647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>341269</t>
+          <t>315647</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>83023</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>71309</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>93994</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>50,59%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>43,45%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>57,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>74233</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>64427</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>85173</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>46,28%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>40,17%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>53,11%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>89692</t>
+          <t>76252</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77955</t>
+          <t>65666</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101177</t>
+          <t>87386</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>163926</t>
+          <t>159276</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>147131</t>
+          <t>144270</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>178956</t>
+          <t>174736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,97%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81087</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>70116</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>92801</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>49,41%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>42,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>56,55%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>86151</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>75211</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>95957</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>53,72%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>46,89%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>59,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>85440</t>
+          <t>83403</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73955</t>
+          <t>72269</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97177</t>
+          <t>93989</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>171590</t>
+          <t>164489</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156560</t>
+          <t>149029</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>188385</t>
+          <t>179495</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>55,44%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>164110</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>164110</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>164110</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>160384</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>160384</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>160384</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>175132</t>
+          <t>159655</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>175132</t>
+          <t>159655</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>175132</t>
+          <t>159655</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>335516</t>
+          <t>323765</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>335516</t>
+          <t>323765</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>335516</t>
+          <t>323765</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>343094</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>318777</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>369021</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>50,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>46,79%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>54,16%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>448</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>307072</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>286377</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>329456</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>49,64%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>46,3%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53,26%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>376082</t>
+          <t>299151</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>348861</t>
+          <t>278773</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>404445</t>
+          <t>321070</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>683154</t>
+          <t>642245</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>646341</t>
+          <t>610007</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>719224</t>
+          <t>672454</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,2%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>338247</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>312320</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>362564</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>49,64%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>45,84%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>53,21%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>458</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>311493</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>289109</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>332188</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>50,36%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>46,74%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>53,7%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>362962</t>
+          <t>307626</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>334599</t>
+          <t>285707</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>390183</t>
+          <t>328004</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>674455</t>
+          <t>645872</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>638385</t>
+          <t>615663</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>711268</t>
+          <t>678110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>681341</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>906</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>618565</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>618565</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>618565</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>932</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>606777</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>606777</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>739044</t>
+          <t>606777</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1357609</t>
+          <t>1288117</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1357609</t>
+          <t>1288117</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1357609</t>
+          <t>1288117</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
